--- a/sources/table_normalization/xlsx/food-table11.xlsx
+++ b/sources/table_normalization/xlsx/food-table11.xlsx
@@ -439,17 +439,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -459,6 +453,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="27">
@@ -799,44 +799,44 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="14.4" customHeight="1">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="18" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="20" t="s">
+      <c r="G3" s="20"/>
+      <c r="H3" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="19"/>
+      <c r="E4" s="17"/>
       <c r="F4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="19"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="6">
